--- a/public/documents/pieces-reponse-2/R2-coefficient-revente.xlsx
+++ b/public/documents/pieces-reponse-2/R2-coefficient-revente.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cascade" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coefficient" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confrontation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methode" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Annuel" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tableau p34" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methode" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +46,9 @@
     <font>
       <i val="1"/>
       <color rgb="007A2E1E"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -95,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -160,6 +165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,11 +548,6 @@
           <t>PIECE R2 — COEFFICIENT DE REVENTE : sources brutes (valeurs en dur, citees). Les onglets suivants ne contiennent que des FORMULES renvoyant a ces cellules.</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -980,9 +981,6 @@
           <t>Bilan matiere des 10 622 L (R1-cascade-bilan-matiere.xlsx). La part revendue est le SEUL chiffre decisif ; elle est ici DERIVEE par formule.</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1282,10 +1280,6 @@
           <t>Du coefficient sur achat revendu au coefficient sur la totalite des achats. Tout est DERIVE par formule des onglets Sources et Cascade.</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1462,10 +1456,6 @@
           <t>Le calcul du service et le meme calcul avec la part mesuree</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1606,14 +1596,6 @@
           <t>Test de la page 93 : coef applique au cout des matieres de chaque exercice. Repere service 3,2725 ; repere mesure = coef sur totalite (2,383251).</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1826,6 +1808,526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Repartition INDICATIVE par exercice du coefficient sur achat revendu. La part revendue (60,77 %) n'est mesuree qu'en cumul 3 ans : la ventilation ci-dessous est un PRORATA des factures d'alcool, pas une mesure annuelle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Achats d'alcool factures FCBS par exercice (bière + vin/cidre + spiritueux/liqueur, HT brut, src/data/calculsBoissons/achatsBoissonsParPeriode.json)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>Exercice</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>Factures alcool HT brut (EUR)</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>Part de l exercice (=formule)</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Cout alcool retenu 107 924 x part (=formule)</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>Cout alcool REVENDU = cout x 60,77 % (=formule)</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>CA alcool encaisse (annexe D, TVA 20 %)</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Coef sur achat REVENDU (=formule)</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>Coef sur la TOTALITE des achats (=formule)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2022-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>36963.72</v>
+      </c>
+      <c r="C5">
+        <f>B5/$B$8</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>Sources!$B$7*C5</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>D5*Cascade!$B$18</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>Sources!B4</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>F5/E5</f>
+        <v/>
+      </c>
+      <c r="H5">
+        <f>F5/D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>37969.83</v>
+      </c>
+      <c r="C6">
+        <f>B6/$B$8</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>Sources!$B$7*C6</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>D6*Cascade!$B$18</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>Sources!B5</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>F6/E6</f>
+        <v/>
+      </c>
+      <c r="H6">
+        <f>F6/D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>38063</v>
+      </c>
+      <c r="C7">
+        <f>B7/$B$8</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>Sources!$B$7*C7</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>D7*Cascade!$B$18</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>Sources!B6</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>F7/E7</f>
+        <v/>
+      </c>
+      <c r="H7">
+        <f>F7/D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>GLOBALISE 3 ans (seule MESURE)</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>SUM(D5:D7)</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>SUM(E5:E7)</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>F8/E8</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>F8/D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lecture : par exercice, le coefficient sur la TOTALITE des achats d'alcool (colonne H) suit les coefficients globaux declares releves par le service p. 56 (2,30 / 2,39 / 2,31) et ceux du memoire du 10/07/2026 pour la boisson (2,35 / 2,49 / 2,44).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Limite : la ligne 8 est la seule mesure (257 209,96 / 65 585 = 3,92 ; 257 209,96 / 107 924 = 2,383251). Les lignes 5 a 7 supposent une part revendue identique chaque annee ; elles ne sont pas opposees comme coefficients annuels mesures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ecart 112 996,55 (factures brutes 3 categories) vs 107 924 (cout d'alcool retenu, boissonsPageData.json) : le prorata porte sur les PARTS (col. C), le montant total reste 107 924.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Controle arithmetique du tableau du service, proposition du 18/05/2026 p. 34 (repris p. 35 avec le CA reconstitue). Valeurs lues sur la page scannee ; totaux recalcules par formule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Ligne du tableau p. 34</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Exercice clos 31/03/2023</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>Exercice clos 31/03/2024</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>Exercice clos 31/03/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TOTAL CHIFFRE D AFFAIRES TTC (inclus 706 800 pourboires)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>404030.87</v>
+      </c>
+      <c r="C4" t="n">
+        <v>438658.43</v>
+      </c>
+      <c r="D4" t="n">
+        <v>435524.92</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Compte 601 100 - Achats denrees</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>127473.87</v>
+      </c>
+      <c r="C5" t="n">
+        <v>137971.41</v>
+      </c>
+      <c r="D5" t="n">
+        <v>142129.11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Compte 601 200 - Achats boissons</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>48237.09</v>
+      </c>
+      <c r="C6" t="n">
+        <v>46384.45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>47098.84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Variation stocks denrees (signe du tableau)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>526.38</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1646.54</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-430.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Variation stocks boissons (signe du tableau)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-800.83</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1029.67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-273.41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cout d achats des matieres ECRIT par le service</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>175436.51</v>
+      </c>
+      <c r="C9" t="n">
+        <v>183679.65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>188544.29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Cout d achats RECALCULE = 601100 + 601200 + variations (=formule)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>SUM(C5:C8)</f>
+        <v/>
+      </c>
+      <c r="D10">
+        <f>SUM(D5:D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ECART ecrit - recalcule (=formule) : 0 attendu</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>B9-B10</f>
+        <v/>
+      </c>
+      <c r="C11">
+        <f>C9-C10</f>
+        <v/>
+      </c>
+      <c r="D11">
+        <f>D9-D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Coefficient declare, tel que le service l ecrit (CA / cout ecrit)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>B4/B9</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>C4/C9</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>D4/D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Coefficient declare, sur le cout recalcule (=formule)</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>B4/B10</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>C4/C10</f>
+        <v/>
+      </c>
+      <c r="D14">
+        <f>D4/D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CA reconstitue par le service (p. 35)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>597265.42</v>
+      </c>
+      <c r="C16" t="n">
+        <v>577522</v>
+      </c>
+      <c r="D16" t="n">
+        <v>575252.6800000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Coefficient reconstitue, tel que le service l ecrit (p. 35 : 3,404 / 3,144 / 3,051)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>B16/B9</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>C16/C9</f>
+        <v/>
+      </c>
+      <c r="D17">
+        <f>D16/D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coefficient reconstitue, sur le cout recalcule (=formule)</t>
+        </is>
+      </c>
+      <c r="B18">
+        <f>B16/B10</f>
+        <v/>
+      </c>
+      <c r="C18">
+        <f>C16/C10</f>
+        <v/>
+      </c>
+      <c r="D18">
+        <f>D16/D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Lecture : sur 2023-2024 le total ecrit (183 679,65) depasse de 2 000,00 EUR la somme de ses propres lignes (181 679,65) ; sur 2024-2025 l ecart est de 20,00 EUR. Le coefficient declare 2023-2024 ressort a 2,414 et non 2,388 ; le reconstitue a 3,179 et non 3,144. Sans incidence sur la demonstration de la page (tests conduits sur les chiffres du service tels quels), mais le tableau fondant le grief ne s additionne pas.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
